--- a/data/code_book.xlsx
+++ b/data/code_book.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericfoerster/Desktop/torv-reports/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericfoerster/Desktop/torv-reports v4/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D23FD2F-0906-D241-ABFC-AADBE4DE600E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962B51C3-640A-F947-A2AC-9D59FFF194BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18100" yWindow="500" windowWidth="22820" windowHeight="26600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22340" yWindow="500" windowWidth="22820" windowHeight="26600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="client_list" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="1134">
   <si>
     <t>client_number</t>
   </si>
@@ -3411,6 +3411,24 @@
   </si>
   <si>
     <t>DOMINION</t>
+  </si>
+  <si>
+    <t>Adobe Creek National Golf Course</t>
+  </si>
+  <si>
+    <t>Chipeta Golf Course</t>
+  </si>
+  <si>
+    <t>S022</t>
+  </si>
+  <si>
+    <t>Organic Matter % at 440C and Sand Fractions</t>
+  </si>
+  <si>
+    <t>ADOBE</t>
+  </si>
+  <si>
+    <t>CHIPETA</t>
   </si>
 </sst>
 </file>
@@ -3980,9 +3998,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4020,7 +4038,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4126,7 +4144,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4268,7 +4286,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4276,7 +4294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -4569,6 +4587,22 @@
       </c>
       <c r="B36" t="s">
         <v>1126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>92138</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>92128</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1129</v>
       </c>
     </row>
   </sheetData>
@@ -4586,7 +4620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B614"/>
+  <dimension ref="A1:B615"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -9457,6 +9491,14 @@
       </c>
       <c r="B614" t="s">
         <v>1057</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A615" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1131</v>
       </c>
     </row>
   </sheetData>
@@ -9680,7 +9722,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8789E2A9-FDC3-4E71-8044-B16DA9DC3A5E}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -10150,6 +10192,28 @@
         <v>1072</v>
       </c>
     </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1072</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/code_book.xlsx
+++ b/data/code_book.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericfoerster/Desktop/torv-reports v4/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962B51C3-640A-F947-A2AC-9D59FFF194BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FAB48B-6453-C847-BC4C-58C412AB0580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22340" yWindow="500" windowWidth="22820" windowHeight="26600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="500" windowWidth="22820" windowHeight="26280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="client_list" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="1141">
   <si>
     <t>client_number</t>
   </si>
@@ -3429,6 +3429,27 @@
   </si>
   <si>
     <t>CHIPETA</t>
+  </si>
+  <si>
+    <t>BD Landscape Contractors</t>
+  </si>
+  <si>
+    <t>Landscape Art Inc</t>
+  </si>
+  <si>
+    <t>Lanscape</t>
+  </si>
+  <si>
+    <t>BDLAND</t>
+  </si>
+  <si>
+    <t>LANDART</t>
+  </si>
+  <si>
+    <t>Town of Basalt</t>
+  </si>
+  <si>
+    <t>BASALT</t>
   </si>
 </sst>
 </file>
@@ -4294,7 +4315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -4603,6 +4624,30 @@
       </c>
       <c r="B38" t="s">
         <v>1129</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>73293</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>91091</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>46061</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1139</v>
       </c>
     </row>
   </sheetData>
@@ -9722,7 +9767,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8789E2A9-FDC3-4E71-8044-B16DA9DC3A5E}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -10214,6 +10259,39 @@
         <v>1072</v>
       </c>
     </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1136</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/code_book.xlsx
+++ b/data/code_book.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericfoerster/Desktop/ torv-reports v4/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F1376C-5820-994D-A1AD-D05055FB1FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DE4CDA-489C-1144-B29A-96FBF3B7AC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13460" yWindow="1040" windowWidth="22820" windowHeight="26280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19560" yWindow="620" windowWidth="22820" windowHeight="26060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="client_list" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="1156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="1157">
   <si>
     <t>client_number</t>
   </si>
@@ -3476,9 +3476,6 @@
     <t>Agriculture</t>
   </si>
   <si>
-    <t>Turf</t>
-  </si>
-  <si>
     <t>Crown Mountain Park</t>
   </si>
   <si>
@@ -3495,6 +3492,12 @@
   </si>
   <si>
     <t>RIFLE</t>
+  </si>
+  <si>
+    <t>SCD Holdings</t>
+  </si>
+  <si>
+    <t>SCD</t>
   </si>
 </sst>
 </file>
@@ -4360,7 +4363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -4732,7 +4735,7 @@
         <v>93893</v>
       </c>
       <c r="B46" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -4740,7 +4743,7 @@
         <v>94002</v>
       </c>
       <c r="B47" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -4748,7 +4751,15 @@
         <v>94252</v>
       </c>
       <c r="B48" t="s">
-        <v>1154</v>
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>94327</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1155</v>
       </c>
     </row>
   </sheetData>
@@ -9868,7 +9879,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8789E2A9-FDC3-4E71-8044-B16DA9DC3A5E}">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -10390,7 +10401,7 @@
         <v>1139</v>
       </c>
       <c r="C47" t="s">
-        <v>1149</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -10439,10 +10450,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B52" t="s">
         <v>1150</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1151</v>
       </c>
       <c r="C52" t="s">
         <v>1076</v>
@@ -10450,10 +10461,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B53" t="s">
         <v>1152</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1153</v>
       </c>
       <c r="C53" t="s">
         <v>1078</v>
@@ -10461,13 +10472,24 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B54" t="s">
         <v>1154</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1155</v>
       </c>
       <c r="C54" t="s">
         <v>1072</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1078</v>
       </c>
     </row>
   </sheetData>

--- a/data/code_book.xlsx
+++ b/data/code_book.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericfoerster/Desktop/ torv-reports v4/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DE4CDA-489C-1144-B29A-96FBF3B7AC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81ACA2CC-2AD0-4E45-BDBF-F7A3FF661AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19560" yWindow="620" windowWidth="22820" windowHeight="26060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16160" yWindow="600" windowWidth="35040" windowHeight="26060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="client_list" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="1157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="1174">
   <si>
     <t>client_number</t>
   </si>
@@ -1541,9 +1541,6 @@
     <t>Standard Soil with Bray II phosphorus and Available Nitrogen (NO3-N + NH4-N)</t>
   </si>
   <si>
-    <t>Standard Soil with SMP/Sikora pH and Available Nitrogen (NO3-N + NH4-N)</t>
-  </si>
-  <si>
     <t>Standard Soil with Olsen phosphorus and Available Nitrogen (NO3-N + NH4-N)</t>
   </si>
   <si>
@@ -3498,6 +3495,60 @@
   </si>
   <si>
     <t>SCD</t>
+  </si>
+  <si>
+    <t>Weihe Engineering Inc</t>
+  </si>
+  <si>
+    <t>WEIHE</t>
+  </si>
+  <si>
+    <t>Standard Soil with SMP Sikora pH and Available Nitrogen (NO3-N + NH4-N)</t>
+  </si>
+  <si>
+    <t>SMP Buffer</t>
+  </si>
+  <si>
+    <t>Landtech Landscape &amp; Maintenance</t>
+  </si>
+  <si>
+    <t>LANDTECH</t>
+  </si>
+  <si>
+    <t>Geneva Golf Club</t>
+  </si>
+  <si>
+    <t>GENEVA</t>
+  </si>
+  <si>
+    <t>SiteOne Landscape Supply &amp; Stone Center</t>
+  </si>
+  <si>
+    <t>SITEONE</t>
+  </si>
+  <si>
+    <t>Ruble Outdoor Concepts</t>
+  </si>
+  <si>
+    <t>RUBLE</t>
+  </si>
+  <si>
+    <t>Siplast</t>
+  </si>
+  <si>
+    <t>SIPLAST</t>
+  </si>
+  <si>
+    <t>bluegreen BLD</t>
+  </si>
+  <si>
+    <t>BLUEGREEN</t>
+  </si>
+  <si>
+    <t>Heritage Landscape Supply</t>
+  </si>
+  <si>
+    <t>HERITAGE</t>
   </si>
 </sst>
 </file>
@@ -4363,7 +4414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -4391,7 +4442,7 @@
         <v>42443</v>
       </c>
       <c r="B3" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -4399,7 +4450,7 @@
         <v>36543</v>
       </c>
       <c r="B4" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -4423,7 +4474,7 @@
         <v>35495</v>
       </c>
       <c r="B7" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -4431,7 +4482,7 @@
         <v>87118</v>
       </c>
       <c r="B8" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -4455,7 +4506,7 @@
         <v>89424</v>
       </c>
       <c r="B11" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -4463,7 +4514,7 @@
         <v>85415</v>
       </c>
       <c r="B12" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -4471,7 +4522,7 @@
         <v>34498</v>
       </c>
       <c r="B13" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -4487,7 +4538,7 @@
         <v>85847</v>
       </c>
       <c r="B15" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -4495,7 +4546,7 @@
         <v>87390</v>
       </c>
       <c r="B16" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -4503,7 +4554,7 @@
         <v>88530</v>
       </c>
       <c r="B17" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -4535,7 +4586,7 @@
         <v>36644</v>
       </c>
       <c r="B21" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4551,7 +4602,7 @@
         <v>76274</v>
       </c>
       <c r="B23" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -4575,7 +4626,7 @@
         <v>88090</v>
       </c>
       <c r="B26" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -4591,7 +4642,7 @@
         <v>43142</v>
       </c>
       <c r="B28" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -4599,7 +4650,7 @@
         <v>83008</v>
       </c>
       <c r="B29" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4639,7 +4690,7 @@
         <v>89973</v>
       </c>
       <c r="B34" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -4647,7 +4698,7 @@
         <v>90182</v>
       </c>
       <c r="B35" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -4655,7 +4706,7 @@
         <v>90668</v>
       </c>
       <c r="B36" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -4663,7 +4714,7 @@
         <v>92138</v>
       </c>
       <c r="B37" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -4671,7 +4722,7 @@
         <v>92128</v>
       </c>
       <c r="B38" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -4679,7 +4730,7 @@
         <v>73293</v>
       </c>
       <c r="B39" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -4687,7 +4738,7 @@
         <v>91091</v>
       </c>
       <c r="B40" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -4695,7 +4746,7 @@
         <v>46061</v>
       </c>
       <c r="B41" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -4703,7 +4754,7 @@
         <v>85137</v>
       </c>
       <c r="B42" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -4711,7 +4762,7 @@
         <v>93470</v>
       </c>
       <c r="B43" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -4719,7 +4770,7 @@
         <v>74400</v>
       </c>
       <c r="B44" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
@@ -4727,7 +4778,7 @@
         <v>93769</v>
       </c>
       <c r="B45" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -4735,7 +4786,7 @@
         <v>93893</v>
       </c>
       <c r="B46" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -4743,7 +4794,7 @@
         <v>94002</v>
       </c>
       <c r="B47" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -4751,7 +4802,7 @@
         <v>94252</v>
       </c>
       <c r="B48" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -4759,7 +4810,68 @@
         <v>94327</v>
       </c>
       <c r="B49" t="s">
-        <v>1155</v>
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>95196</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>95618</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>30368</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>95991</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>95687</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>95661</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>96064</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>1172</v>
       </c>
     </row>
   </sheetData>
@@ -4782,10 +4894,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B1" t="s">
         <v>1048</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -4849,7 +4961,7 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>504</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -4857,7 +4969,7 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>504</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -4865,7 +4977,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -4873,7 +4985,7 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -4881,7 +4993,7 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -4889,7 +5001,7 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -4897,7 +5009,7 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -4905,7 +5017,7 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -4913,7 +5025,7 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -4921,7 +5033,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -4929,7 +5041,7 @@
         <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -4937,7 +5049,7 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -4945,7 +5057,7 @@
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4953,7 +5065,7 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4961,7 +5073,7 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -4969,7 +5081,7 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -4977,7 +5089,7 @@
         <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -4985,7 +5097,7 @@
         <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -4993,7 +5105,7 @@
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -5001,7 +5113,7 @@
         <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -5009,7 +5121,7 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -5017,7 +5129,7 @@
         <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -5025,7 +5137,7 @@
         <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -5033,7 +5145,7 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -5041,7 +5153,7 @@
         <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -5529,7 +5641,7 @@
         <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
@@ -5537,7 +5649,7 @@
         <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -5865,7 +5977,7 @@
         <v>254</v>
       </c>
       <c r="B136" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
@@ -5873,7 +5985,7 @@
         <v>255</v>
       </c>
       <c r="B137" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
@@ -5881,7 +5993,7 @@
         <v>256</v>
       </c>
       <c r="B138" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
@@ -6169,7 +6281,7 @@
         <v>309</v>
       </c>
       <c r="B174" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
@@ -6177,7 +6289,7 @@
         <v>310</v>
       </c>
       <c r="B175" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
@@ -6185,7 +6297,7 @@
         <v>311</v>
       </c>
       <c r="B176" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
@@ -6193,7 +6305,7 @@
         <v>312</v>
       </c>
       <c r="B177" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
@@ -6201,7 +6313,7 @@
         <v>313</v>
       </c>
       <c r="B178" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
@@ -6209,7 +6321,7 @@
         <v>314</v>
       </c>
       <c r="B179" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
@@ -6457,7 +6569,7 @@
         <v>361</v>
       </c>
       <c r="B210" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
@@ -6465,7 +6577,7 @@
         <v>362</v>
       </c>
       <c r="B211" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
@@ -6673,7 +6785,7 @@
         <v>396</v>
       </c>
       <c r="B237" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
@@ -6681,7 +6793,7 @@
         <v>397</v>
       </c>
       <c r="B238" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
@@ -6689,7 +6801,7 @@
         <v>398</v>
       </c>
       <c r="B239" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
@@ -6697,7 +6809,7 @@
         <v>399</v>
       </c>
       <c r="B240" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
@@ -6993,7 +7105,7 @@
         <v>447</v>
       </c>
       <c r="B277" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
@@ -7001,7 +7113,7 @@
         <v>448</v>
       </c>
       <c r="B278" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
@@ -7094,7 +7206,7 @@
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B290" t="s">
         <v>235</v>
@@ -7137,7 +7249,7 @@
         <v>466</v>
       </c>
       <c r="B295" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
@@ -7145,7 +7257,7 @@
         <v>467</v>
       </c>
       <c r="B296" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
@@ -7153,7 +7265,7 @@
         <v>468</v>
       </c>
       <c r="B297" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
@@ -7161,7 +7273,7 @@
         <v>469</v>
       </c>
       <c r="B298" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
@@ -7367,935 +7479,935 @@
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B326" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B327" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B328" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
+        <v>577</v>
+      </c>
+      <c r="B329" t="s">
         <v>578</v>
-      </c>
-      <c r="B329" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
+        <v>579</v>
+      </c>
+      <c r="B330" t="s">
         <v>580</v>
-      </c>
-      <c r="B330" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
+        <v>581</v>
+      </c>
+      <c r="B331" t="s">
         <v>582</v>
-      </c>
-      <c r="B331" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
+        <v>583</v>
+      </c>
+      <c r="B332" t="s">
         <v>584</v>
-      </c>
-      <c r="B332" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
+        <v>589</v>
+      </c>
+      <c r="B333" t="s">
         <v>590</v>
-      </c>
-      <c r="B333" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
+        <v>591</v>
+      </c>
+      <c r="B334" t="s">
         <v>592</v>
-      </c>
-      <c r="B334" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
+        <v>593</v>
+      </c>
+      <c r="B335" t="s">
         <v>594</v>
-      </c>
-      <c r="B335" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
+        <v>595</v>
+      </c>
+      <c r="B336" t="s">
         <v>596</v>
-      </c>
-      <c r="B336" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
+        <v>597</v>
+      </c>
+      <c r="B337" t="s">
         <v>598</v>
-      </c>
-      <c r="B337" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B338" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B339" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B340" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B341" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B342" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B343" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B344" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
+        <v>608</v>
+      </c>
+      <c r="B345" t="s">
         <v>609</v>
-      </c>
-      <c r="B345" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B346" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B347" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
+        <v>612</v>
+      </c>
+      <c r="B348" t="s">
         <v>613</v>
-      </c>
-      <c r="B348" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
+        <v>614</v>
+      </c>
+      <c r="B349" t="s">
         <v>615</v>
-      </c>
-      <c r="B349" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
+        <v>616</v>
+      </c>
+      <c r="B350" t="s">
         <v>617</v>
-      </c>
-      <c r="B350" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
+        <v>618</v>
+      </c>
+      <c r="B351" t="s">
         <v>619</v>
-      </c>
-      <c r="B351" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
+        <v>620</v>
+      </c>
+      <c r="B352" t="s">
         <v>621</v>
-      </c>
-      <c r="B352" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
+        <v>622</v>
+      </c>
+      <c r="B353" t="s">
         <v>623</v>
-      </c>
-      <c r="B353" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
+        <v>624</v>
+      </c>
+      <c r="B354" t="s">
         <v>625</v>
-      </c>
-      <c r="B354" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
+        <v>626</v>
+      </c>
+      <c r="B355" t="s">
         <v>627</v>
-      </c>
-      <c r="B355" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
+        <v>628</v>
+      </c>
+      <c r="B356" t="s">
         <v>629</v>
-      </c>
-      <c r="B356" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
+        <v>630</v>
+      </c>
+      <c r="B357" t="s">
         <v>631</v>
-      </c>
-      <c r="B357" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
+        <v>632</v>
+      </c>
+      <c r="B358" t="s">
         <v>633</v>
-      </c>
-      <c r="B358" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
+        <v>634</v>
+      </c>
+      <c r="B359" t="s">
         <v>635</v>
-      </c>
-      <c r="B359" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
+        <v>636</v>
+      </c>
+      <c r="B360" t="s">
         <v>637</v>
-      </c>
-      <c r="B360" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
+        <v>643</v>
+      </c>
+      <c r="B361" t="s">
         <v>644</v>
-      </c>
-      <c r="B361" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
+        <v>647</v>
+      </c>
+      <c r="B362" t="s">
         <v>648</v>
-      </c>
-      <c r="B362" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B363" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
+        <v>652</v>
+      </c>
+      <c r="B364" t="s">
         <v>653</v>
-      </c>
-      <c r="B364" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
+        <v>552</v>
+      </c>
+      <c r="B365" t="s">
         <v>553</v>
-      </c>
-      <c r="B365" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
+        <v>554</v>
+      </c>
+      <c r="B366" t="s">
         <v>555</v>
-      </c>
-      <c r="B366" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
+        <v>556</v>
+      </c>
+      <c r="B367" t="s">
         <v>557</v>
-      </c>
-      <c r="B367" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
+        <v>558</v>
+      </c>
+      <c r="B368" t="s">
         <v>559</v>
-      </c>
-      <c r="B368" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
+        <v>550</v>
+      </c>
+      <c r="B369" t="s">
         <v>551</v>
-      </c>
-      <c r="B369" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
+        <v>664</v>
+      </c>
+      <c r="B370" t="s">
         <v>665</v>
-      </c>
-      <c r="B370" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
+        <v>667</v>
+      </c>
+      <c r="B371" t="s">
         <v>668</v>
-      </c>
-      <c r="B371" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
+        <v>669</v>
+      </c>
+      <c r="B372" t="s">
         <v>670</v>
-      </c>
-      <c r="B372" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
+        <v>560</v>
+      </c>
+      <c r="B373" t="s">
         <v>561</v>
-      </c>
-      <c r="B373" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
+        <v>567</v>
+      </c>
+      <c r="B374" t="s">
         <v>568</v>
-      </c>
-      <c r="B374" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
+        <v>563</v>
+      </c>
+      <c r="B375" t="s">
         <v>564</v>
-      </c>
-      <c r="B375" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
+        <v>673</v>
+      </c>
+      <c r="B376" t="s">
         <v>674</v>
-      </c>
-      <c r="B376" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
+        <v>675</v>
+      </c>
+      <c r="B377" t="s">
         <v>676</v>
-      </c>
-      <c r="B377" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
+        <v>677</v>
+      </c>
+      <c r="B378" t="s">
         <v>678</v>
-      </c>
-      <c r="B378" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B379" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
+        <v>682</v>
+      </c>
+      <c r="B380" t="s">
         <v>683</v>
-      </c>
-      <c r="B380" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
+        <v>585</v>
+      </c>
+      <c r="B381" t="s">
         <v>586</v>
-      </c>
-      <c r="B381" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
+        <v>587</v>
+      </c>
+      <c r="B382" t="s">
         <v>588</v>
-      </c>
-      <c r="B382" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A383" s="1"/>
       <c r="B383" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A384" s="1"/>
       <c r="B384" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B385" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B386" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B387" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B388" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B389" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B390" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B391" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
+        <v>719</v>
+      </c>
+      <c r="B392" t="s">
         <v>720</v>
-      </c>
-      <c r="B392" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B393" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B394" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
+        <v>638</v>
+      </c>
+      <c r="B395" t="s">
         <v>639</v>
-      </c>
-      <c r="B395" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
+        <v>640</v>
+      </c>
+      <c r="B396" t="s">
         <v>641</v>
-      </c>
-      <c r="B396" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
+        <v>650</v>
+      </c>
+      <c r="B397" t="s">
         <v>651</v>
-      </c>
-      <c r="B397" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
+        <v>654</v>
+      </c>
+      <c r="B398" t="s">
         <v>655</v>
-      </c>
-      <c r="B398" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
+        <v>565</v>
+      </c>
+      <c r="B399" t="s">
         <v>566</v>
-      </c>
-      <c r="B399" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
+        <v>671</v>
+      </c>
+      <c r="B400" t="s">
         <v>672</v>
-      </c>
-      <c r="B400" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
+        <v>724</v>
+      </c>
+      <c r="B401" t="s">
         <v>725</v>
-      </c>
-      <c r="B401" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
+        <v>691</v>
+      </c>
+      <c r="B402" t="s">
         <v>692</v>
-      </c>
-      <c r="B402" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B403" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
+        <v>687</v>
+      </c>
+      <c r="B404" t="s">
         <v>688</v>
-      </c>
-      <c r="B404" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
+        <v>689</v>
+      </c>
+      <c r="B405" t="s">
         <v>690</v>
-      </c>
-      <c r="B405" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A406" s="1"/>
       <c r="B406" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
+        <v>728</v>
+      </c>
+      <c r="B407" t="s">
         <v>729</v>
-      </c>
-      <c r="B407" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
+        <v>735</v>
+      </c>
+      <c r="B408" t="s">
         <v>736</v>
-      </c>
-      <c r="B408" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
+        <v>737</v>
+      </c>
+      <c r="B409" t="s">
         <v>738</v>
-      </c>
-      <c r="B409" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
+        <v>739</v>
+      </c>
+      <c r="B410" t="s">
         <v>740</v>
-      </c>
-      <c r="B410" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B411" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B412" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B413" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B414" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B415" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B416" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
+        <v>743</v>
+      </c>
+      <c r="B417" t="s">
         <v>744</v>
-      </c>
-      <c r="B417" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
+        <v>745</v>
+      </c>
+      <c r="B418" t="s">
         <v>746</v>
-      </c>
-      <c r="B418" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
+        <v>747</v>
+      </c>
+      <c r="B419" t="s">
         <v>748</v>
-      </c>
-      <c r="B419" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B420" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B421" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B422" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
+        <v>752</v>
+      </c>
+      <c r="B423" t="s">
         <v>753</v>
-      </c>
-      <c r="B423" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
+        <v>754</v>
+      </c>
+      <c r="B424" t="s">
         <v>755</v>
-      </c>
-      <c r="B424" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
+        <v>756</v>
+      </c>
+      <c r="B425" t="s">
         <v>757</v>
-      </c>
-      <c r="B425" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
+        <v>758</v>
+      </c>
+      <c r="B426" t="s">
         <v>759</v>
-      </c>
-      <c r="B426" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
+        <v>760</v>
+      </c>
+      <c r="B427" t="s">
         <v>761</v>
-      </c>
-      <c r="B427" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
+        <v>762</v>
+      </c>
+      <c r="B428" t="s">
         <v>763</v>
-      </c>
-      <c r="B428" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
+        <v>764</v>
+      </c>
+      <c r="B429" t="s">
         <v>765</v>
-      </c>
-      <c r="B429" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
+        <v>766</v>
+      </c>
+      <c r="B430" t="s">
         <v>767</v>
-      </c>
-      <c r="B430" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
+        <v>768</v>
+      </c>
+      <c r="B431" t="s">
         <v>769</v>
-      </c>
-      <c r="B431" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
+        <v>770</v>
+      </c>
+      <c r="B432" t="s">
         <v>771</v>
-      </c>
-      <c r="B432" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
+        <v>772</v>
+      </c>
+      <c r="B433" t="s">
         <v>773</v>
-      </c>
-      <c r="B433" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
+        <v>774</v>
+      </c>
+      <c r="B434" t="s">
         <v>775</v>
-      </c>
-      <c r="B434" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
+        <v>776</v>
+      </c>
+      <c r="B435" t="s">
         <v>777</v>
-      </c>
-      <c r="B435" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
+        <v>778</v>
+      </c>
+      <c r="B436" t="s">
         <v>779</v>
-      </c>
-      <c r="B436" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
+        <v>780</v>
+      </c>
+      <c r="B437" t="s">
         <v>781</v>
-      </c>
-      <c r="B437" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
+        <v>782</v>
+      </c>
+      <c r="B438" t="s">
         <v>783</v>
-      </c>
-      <c r="B438" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
+        <v>784</v>
+      </c>
+      <c r="B439" t="s">
         <v>785</v>
-      </c>
-      <c r="B439" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
+        <v>786</v>
+      </c>
+      <c r="B440" t="s">
         <v>787</v>
-      </c>
-      <c r="B440" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
+        <v>788</v>
+      </c>
+      <c r="B441" t="s">
         <v>789</v>
-      </c>
-      <c r="B441" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
@@ -8303,1108 +8415,1108 @@
         <v>19</v>
       </c>
       <c r="B442" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
+        <v>791</v>
+      </c>
+      <c r="B443" t="s">
         <v>792</v>
-      </c>
-      <c r="B443" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B444" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B445" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B446" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
+        <v>732</v>
+      </c>
+      <c r="B447" t="s">
         <v>733</v>
-      </c>
-      <c r="B447" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
+        <v>645</v>
+      </c>
+      <c r="B448" t="s">
         <v>646</v>
-      </c>
-      <c r="B448" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
+        <v>662</v>
+      </c>
+      <c r="B449" t="s">
         <v>663</v>
-      </c>
-      <c r="B449" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
+        <v>547</v>
+      </c>
+      <c r="B450" t="s">
         <v>548</v>
-      </c>
-      <c r="B450" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
+        <v>656</v>
+      </c>
+      <c r="B451" t="s">
         <v>657</v>
-      </c>
-      <c r="B451" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
+        <v>658</v>
+      </c>
+      <c r="B452" t="s">
         <v>659</v>
-      </c>
-      <c r="B452" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
+        <v>660</v>
+      </c>
+      <c r="B453" t="s">
         <v>661</v>
-      </c>
-      <c r="B453" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
+        <v>679</v>
+      </c>
+      <c r="B454" t="s">
         <v>680</v>
-      </c>
-      <c r="B454" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
+        <v>684</v>
+      </c>
+      <c r="B455" t="s">
         <v>685</v>
-      </c>
-      <c r="B455" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
+        <v>569</v>
+      </c>
+      <c r="B456" t="s">
         <v>570</v>
-      </c>
-      <c r="B456" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B457" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
+        <v>694</v>
+      </c>
+      <c r="B458" t="s">
         <v>695</v>
-      </c>
-      <c r="B458" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
+        <v>696</v>
+      </c>
+      <c r="B459" t="s">
         <v>697</v>
-      </c>
-      <c r="B459" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
+        <v>698</v>
+      </c>
+      <c r="B460" t="s">
         <v>699</v>
-      </c>
-      <c r="B460" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
+        <v>700</v>
+      </c>
+      <c r="B461" t="s">
         <v>701</v>
-      </c>
-      <c r="B461" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
+        <v>702</v>
+      </c>
+      <c r="B462" t="s">
         <v>703</v>
-      </c>
-      <c r="B462" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B463" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B464" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
+        <v>706</v>
+      </c>
+      <c r="B465" t="s">
         <v>707</v>
-      </c>
-      <c r="B465" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B466" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
+        <v>795</v>
+      </c>
+      <c r="B467" t="s">
         <v>796</v>
-      </c>
-      <c r="B467" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
+        <v>797</v>
+      </c>
+      <c r="B468" t="s">
         <v>798</v>
-      </c>
-      <c r="B468" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
+        <v>801</v>
+      </c>
+      <c r="B469" t="s">
         <v>802</v>
-      </c>
-      <c r="B469" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B470" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B471" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B472" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B473" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B474" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B475" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B476" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B477" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B478" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B479" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B480" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B481" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B482" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B483" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B484" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B485" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B486" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A487" s="1"/>
       <c r="B487" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B488" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B489" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B490" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B491" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B492" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B493" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B494" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A495" s="1"/>
       <c r="B495" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B496" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B497" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B498" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B499" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B500" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B501" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B502" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A503" s="1"/>
       <c r="B503" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B504" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B505" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B506" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B507" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B508" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B509" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
+        <v>839</v>
+      </c>
+      <c r="B510" t="s">
         <v>840</v>
-      </c>
-      <c r="B510" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A511" s="1"/>
       <c r="B511" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
+        <v>841</v>
+      </c>
+      <c r="B512" t="s">
         <v>842</v>
-      </c>
-      <c r="B512" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A513" s="1"/>
       <c r="B513" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B514" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B515" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B516" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B517" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B518" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B519" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B520" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B521" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
+        <v>851</v>
+      </c>
+      <c r="B522" t="s">
         <v>852</v>
-      </c>
-      <c r="B522" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" s="1"/>
       <c r="B523" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B524" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" s="1"/>
       <c r="B525" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B526" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B527" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B528" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B529" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B530" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B531" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B532" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B533" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B534" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B535" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B536" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B537" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B538" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B539" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B540" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B541" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B542" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" s="1"/>
       <c r="B543" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B544" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B545" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B546" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" s="1"/>
       <c r="B547" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B548" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B549" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B550" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B551" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B552" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B553" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" s="1"/>
       <c r="B554" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B555" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B556" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B557" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B558" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
+        <v>881</v>
+      </c>
+      <c r="B559" t="s">
         <v>882</v>
-      </c>
-      <c r="B559" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" s="1"/>
       <c r="B560" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B561" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" s="1"/>
       <c r="B562" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B563" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B564" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
+        <v>886</v>
+      </c>
+      <c r="B565" t="s">
         <v>887</v>
-      </c>
-      <c r="B565" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" s="1"/>
       <c r="B566" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B567" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B568" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
+        <v>889</v>
+      </c>
+      <c r="B569" t="s">
         <v>890</v>
-      </c>
-      <c r="B569" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A570" s="1"/>
       <c r="B570" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
+        <v>891</v>
+      </c>
+      <c r="B571" t="s">
         <v>892</v>
-      </c>
-      <c r="B571" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A572" s="1"/>
       <c r="B572" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
+        <v>893</v>
+      </c>
+      <c r="B573" t="s">
         <v>894</v>
-      </c>
-      <c r="B573" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A574" s="1"/>
       <c r="B574" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B575" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B576" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B577" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B578" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B579" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B580" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B581" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B582" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
+        <v>940</v>
+      </c>
+      <c r="B583" t="s">
         <v>941</v>
-      </c>
-      <c r="B583" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B584" t="s">
         <v>22</v>
@@ -9412,250 +9524,250 @@
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
+        <v>943</v>
+      </c>
+      <c r="B585" t="s">
         <v>944</v>
-      </c>
-      <c r="B585" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
+        <v>945</v>
+      </c>
+      <c r="B586" t="s">
         <v>946</v>
-      </c>
-      <c r="B586" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
+        <v>947</v>
+      </c>
+      <c r="B587" t="s">
         <v>948</v>
-      </c>
-      <c r="B587" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
+        <v>949</v>
+      </c>
+      <c r="B588" t="s">
         <v>950</v>
-      </c>
-      <c r="B588" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
+        <v>951</v>
+      </c>
+      <c r="B589" t="s">
         <v>952</v>
-      </c>
-      <c r="B589" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
+        <v>953</v>
+      </c>
+      <c r="B590" t="s">
         <v>954</v>
-      </c>
-      <c r="B590" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
+        <v>955</v>
+      </c>
+      <c r="B591" t="s">
         <v>956</v>
-      </c>
-      <c r="B591" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
+        <v>957</v>
+      </c>
+      <c r="B592" t="s">
         <v>958</v>
-      </c>
-      <c r="B592" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
+        <v>959</v>
+      </c>
+      <c r="B593" t="s">
         <v>960</v>
-      </c>
-      <c r="B593" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
+        <v>961</v>
+      </c>
+      <c r="B594" t="s">
         <v>962</v>
-      </c>
-      <c r="B594" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
+        <v>963</v>
+      </c>
+      <c r="B595" t="s">
         <v>964</v>
-      </c>
-      <c r="B595" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
+        <v>965</v>
+      </c>
+      <c r="B596" t="s">
         <v>966</v>
-      </c>
-      <c r="B596" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
+        <v>967</v>
+      </c>
+      <c r="B597" t="s">
         <v>968</v>
-      </c>
-      <c r="B597" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
+        <v>969</v>
+      </c>
+      <c r="B598" t="s">
         <v>970</v>
-      </c>
-      <c r="B598" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
+        <v>971</v>
+      </c>
+      <c r="B599" t="s">
         <v>972</v>
-      </c>
-      <c r="B599" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
+        <v>973</v>
+      </c>
+      <c r="B600" t="s">
         <v>974</v>
-      </c>
-      <c r="B600" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
+        <v>975</v>
+      </c>
+      <c r="B601" t="s">
         <v>976</v>
-      </c>
-      <c r="B601" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
+        <v>977</v>
+      </c>
+      <c r="B602" t="s">
         <v>978</v>
-      </c>
-      <c r="B602" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
+        <v>979</v>
+      </c>
+      <c r="B603" t="s">
         <v>980</v>
-      </c>
-      <c r="B603" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
+        <v>981</v>
+      </c>
+      <c r="B604" t="s">
         <v>982</v>
-      </c>
-      <c r="B604" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
+        <v>983</v>
+      </c>
+      <c r="B605" t="s">
         <v>984</v>
-      </c>
-      <c r="B605" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
+        <v>985</v>
+      </c>
+      <c r="B606" t="s">
         <v>986</v>
-      </c>
-      <c r="B606" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
+        <v>987</v>
+      </c>
+      <c r="B607" t="s">
         <v>988</v>
-      </c>
-      <c r="B607" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
+        <v>989</v>
+      </c>
+      <c r="B608" t="s">
         <v>990</v>
-      </c>
-      <c r="B608" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
+        <v>991</v>
+      </c>
+      <c r="B609" t="s">
         <v>992</v>
-      </c>
-      <c r="B609" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
+        <v>993</v>
+      </c>
+      <c r="B610" t="s">
         <v>994</v>
-      </c>
-      <c r="B610" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
+        <v>995</v>
+      </c>
+      <c r="B611" t="s">
         <v>996</v>
-      </c>
-      <c r="B611" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
+        <v>997</v>
+      </c>
+      <c r="B612" t="s">
         <v>998</v>
-      </c>
-      <c r="B612" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B613" t="s">
         <v>1054</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B614" t="s">
         <v>1056</v>
-      </c>
-      <c r="B614" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B615" t="s">
         <v>1130</v>
-      </c>
-      <c r="B615" t="s">
-        <v>1131</v>
       </c>
     </row>
   </sheetData>
@@ -9669,207 +9781,216 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B2" t="s">
         <v>1001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="s">
         <v>1003</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B4" t="s">
         <v>1005</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B5" t="s">
         <v>1007</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B6" t="s">
         <v>1009</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B7" t="s">
         <v>1011</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B8" t="s">
         <v>1013</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B9" t="s">
         <v>1015</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B10" t="s">
         <v>1017</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B11" t="s">
         <v>1019</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B12" t="s">
         <v>1021</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B13" t="s">
         <v>1023</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B14" t="s">
         <v>1025</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B15" t="s">
         <v>1027</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B16" t="s">
         <v>1029</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B17" t="s">
         <v>1031</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B18" t="s">
         <v>1033</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B19" t="s">
         <v>1035</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B20" t="s">
         <v>1037</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B21" t="s">
         <v>1039</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B22" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>1042</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B24" t="s">
         <v>1044</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B25" t="s">
         <v>1046</v>
       </c>
-      <c r="B25" t="s">
-        <v>1047</v>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>1159</v>
       </c>
     </row>
   </sheetData>
@@ -9879,7 +10000,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8789E2A9-FDC3-4E71-8044-B16DA9DC3A5E}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -9889,13 +10010,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B1" t="s">
         <v>1068</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1069</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -9903,10 +10024,10 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C2" t="s">
         <v>1071</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -9914,10 +10035,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C3" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -9925,10 +10046,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C4" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -9936,10 +10057,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C5" t="s">
         <v>1075</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -9947,10 +10068,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C6" t="s">
         <v>1077</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -9958,10 +10079,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C7" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -9969,76 +10090,76 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C8" t="s">
         <v>1080</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B9" t="s">
         <v>1082</v>
       </c>
-      <c r="B9" t="s">
-        <v>1083</v>
-      </c>
       <c r="C9" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B10" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C10" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C11" t="s">
         <v>1085</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B12" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C12" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B13" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B14" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C14" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -10046,21 +10167,21 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C15" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B16" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C16" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -10068,21 +10189,21 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C17" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B18" t="s">
         <v>1093</v>
       </c>
-      <c r="B18" t="s">
-        <v>1094</v>
-      </c>
       <c r="C18" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -10090,43 +10211,43 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C19" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B20" t="s">
         <v>1096</v>
       </c>
-      <c r="B20" t="s">
-        <v>1097</v>
-      </c>
       <c r="C20" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B21" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C21" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B22" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C22" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -10134,10 +10255,10 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C23" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -10145,10 +10266,10 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C24" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -10156,10 +10277,10 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C25" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -10167,329 +10288,417 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C26" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B27" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C27" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B28" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C28" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B29" t="s">
         <v>1106</v>
       </c>
-      <c r="B29" t="s">
-        <v>1107</v>
-      </c>
       <c r="C29" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B30" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C30" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B31" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C31" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B32" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C32" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B33" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C33" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B34" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C34" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B35" t="s">
         <v>1113</v>
       </c>
-      <c r="B35" t="s">
-        <v>1114</v>
-      </c>
       <c r="C35" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B36" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C36" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B37" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C37" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B38" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C38" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B39" t="s">
         <v>1117</v>
       </c>
-      <c r="B39" t="s">
-        <v>1118</v>
-      </c>
       <c r="C39" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B40" t="s">
         <v>1122</v>
       </c>
-      <c r="B40" t="s">
-        <v>1123</v>
-      </c>
       <c r="C40" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B41" t="s">
         <v>1124</v>
       </c>
-      <c r="B41" t="s">
-        <v>1125</v>
-      </c>
       <c r="C41" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B42" t="s">
         <v>1126</v>
       </c>
-      <c r="B42" t="s">
-        <v>1127</v>
-      </c>
       <c r="C42" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B43" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C43" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B44" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C44" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B45" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C45" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B46" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C46" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B47" t="s">
         <v>1138</v>
       </c>
-      <c r="B47" t="s">
-        <v>1139</v>
-      </c>
       <c r="C47" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B48" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C48" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B49" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C49" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B50" t="s">
         <v>1144</v>
       </c>
-      <c r="B50" t="s">
-        <v>1145</v>
-      </c>
       <c r="C50" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B51" t="s">
         <v>1146</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>1147</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B52" t="s">
         <v>1149</v>
       </c>
-      <c r="B52" t="s">
-        <v>1150</v>
-      </c>
       <c r="C52" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B53" t="s">
         <v>1151</v>
       </c>
-      <c r="B53" t="s">
-        <v>1152</v>
-      </c>
       <c r="C53" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B54" t="s">
         <v>1153</v>
       </c>
-      <c r="B54" t="s">
-        <v>1154</v>
-      </c>
       <c r="C54" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B55" t="s">
         <v>1155</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>1156</v>
       </c>
-      <c r="C55" t="s">
-        <v>1078</v>
+      <c r="B56" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1077</v>
       </c>
     </row>
   </sheetData>

--- a/data/code_book.xlsx
+++ b/data/code_book.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericfoerster/Desktop/ torv-reports v4/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81ACA2CC-2AD0-4E45-BDBF-F7A3FF661AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B19C74-C0D4-4D47-AAC8-700F3C51142E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16160" yWindow="600" windowWidth="35040" windowHeight="26060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="600" windowWidth="35040" windowHeight="26060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="client_list" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="1178">
   <si>
     <t>client_number</t>
   </si>
@@ -3549,6 +3549,18 @@
   </si>
   <si>
     <t>HERITAGE</t>
+  </si>
+  <si>
+    <t>Sun Valley Resort White Clouds Golf Course</t>
+  </si>
+  <si>
+    <t>Sun Valley Resort Trail Creek Golf Course</t>
+  </si>
+  <si>
+    <t>WHITECLOUDS</t>
+  </si>
+  <si>
+    <t>TRAILCREEK</t>
   </si>
 </sst>
 </file>
@@ -4414,7 +4426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -4870,8 +4882,27 @@
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>96231</v>
+      </c>
       <c r="B57" t="s">
         <v>1172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>96459</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>96461</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1175</v>
       </c>
     </row>
   </sheetData>
@@ -10000,7 +10031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8789E2A9-FDC3-4E71-8044-B16DA9DC3A5E}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -10701,6 +10732,28 @@
         <v>1077</v>
       </c>
     </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1071</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
